--- a/outputs/evaluation/architecture/validation/CF_M06/run_3/CF_M06_arch_eval_by_type.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/run_3/CF_M06_arch_eval_by_type.xlsx
@@ -580,22 +580,22 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4286</v>
+        <v>0.5714</v>
       </c>
     </row>
     <row r="7">
@@ -611,19 +611,19 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
         <v>4</v>
       </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5714</v>
+        <v>0.4286</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8">
